--- a/tame_output/ON/bt/strategyON_20230811.xlsx
+++ b/tame_output/ON/bt/strategyON_20230811.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1685"/>
+  <dimension ref="A1:G1686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40265,7 +40265,7 @@
         <v>45147</v>
       </c>
       <c r="B1685" t="n">
-        <v>2.892115293780109</v>
+        <v>2.891684885919024</v>
       </c>
       <c r="C1685" t="n">
         <v>2.986657920131648</v>
@@ -40281,6 +40281,29 @@
       </c>
       <c r="G1685" t="n">
         <v>4.28831167539576</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="2" t="n">
+        <v>45148</v>
+      </c>
+      <c r="B1686" t="n">
+        <v>2.885818267569</v>
+      </c>
+      <c r="C1686" t="n">
+        <v>2.988521600156002</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>1.540756772320142</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>3.604467884770312</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>2.169003450926559</v>
+      </c>
+      <c r="G1686" t="n">
+        <v>4.289923670711938</v>
       </c>
     </row>
   </sheetData>
